--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1355,6 +1355,2141 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127739100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96702</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>53</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>563005</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6355183</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127739047</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100539</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>562936</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6355216</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127739176</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91964</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>562997</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6355077</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127738729</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92640</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>562900</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6355069</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127738974</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92656</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>562931</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6355226</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127739327</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92656</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>563097</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6355118</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127739045</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92656</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>562936</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6355216</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127739242</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92614</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>563010</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6355064</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127739120</v>
+      </c>
+      <c r="B16" t="n">
+        <v>110334</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>562926</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6355122</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127738760</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91751</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>562898</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6355174</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127739186</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92622</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>563004</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6355079</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127739394</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96702</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>53</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>563102</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6355133</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127739285</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92622</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>563025</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6355088</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127739305</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92656</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>563081</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6355112</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127739175</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92622</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>562997</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6355077</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127739159</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92614</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>562988</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6355078</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127738956</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91964</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>562939</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6355259</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127739160</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92622</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>562988</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6355078</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127738941</v>
+      </c>
+      <c r="B26" t="n">
+        <v>105488</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>562981</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6355301</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127739142</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91964</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>562991</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6355101</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127739079</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92614</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>562951</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6355191</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar inom 1 m2.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127739305</v>
+        <v>127739175</v>
       </c>
       <c r="B21" t="n">
-        <v>92656</v>
+        <v>92622</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563081</v>
+        <v>562997</v>
       </c>
       <c r="R21" t="n">
-        <v>6355112</v>
+        <v>6355077</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2779,10 +2779,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127739175</v>
+        <v>127739305</v>
       </c>
       <c r="B22" t="n">
-        <v>92622</v>
+        <v>92656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2790,21 +2790,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562997</v>
+        <v>563081</v>
       </c>
       <c r="R22" t="n">
-        <v>6355077</v>
+        <v>6355112</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3285,32 +3285,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127739142</v>
+        <v>127739079</v>
       </c>
       <c r="B27" t="n">
-        <v>91964</v>
+        <v>92614</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3323,13 +3323,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562991</v>
+        <v>562951</v>
       </c>
       <c r="R27" t="n">
-        <v>6355101</v>
+        <v>6355191</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3359,6 +3359,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3386,32 +3391,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127739079</v>
+        <v>127739142</v>
       </c>
       <c r="B28" t="n">
-        <v>92614</v>
+        <v>91964</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3424,13 +3429,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562951</v>
+        <v>562991</v>
       </c>
       <c r="R28" t="n">
-        <v>6355191</v>
+        <v>6355101</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3460,11 +3465,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -2475,38 +2475,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127739394</v>
+        <v>127739285</v>
       </c>
       <c r="B19" t="n">
-        <v>96702</v>
+        <v>92622</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2514,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563102</v>
+        <v>563025</v>
       </c>
       <c r="R19" t="n">
-        <v>6355133</v>
+        <v>6355088</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2577,37 +2576,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127739285</v>
+        <v>127739394</v>
       </c>
       <c r="B20" t="n">
-        <v>92622</v>
+        <v>96702</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563025</v>
+        <v>563102</v>
       </c>
       <c r="R20" t="n">
-        <v>6355088</v>
+        <v>6355133</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127739160</v>
+        <v>127738941</v>
       </c>
       <c r="B25" t="n">
-        <v>92622</v>
+        <v>105488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3093,26 +3093,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3120,13 +3121,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562988</v>
+        <v>562981</v>
       </c>
       <c r="R25" t="n">
-        <v>6355078</v>
+        <v>6355301</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3183,10 +3184,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127738941</v>
+        <v>127739160</v>
       </c>
       <c r="B26" t="n">
-        <v>105488</v>
+        <v>92622</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,27 +3195,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3222,13 +3222,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562981</v>
+        <v>562988</v>
       </c>
       <c r="R26" t="n">
-        <v>6355301</v>
+        <v>6355078</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3285,32 +3285,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127739079</v>
+        <v>127739142</v>
       </c>
       <c r="B27" t="n">
-        <v>92614</v>
+        <v>91964</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3323,13 +3323,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562951</v>
+        <v>562991</v>
       </c>
       <c r="R27" t="n">
-        <v>6355191</v>
+        <v>6355101</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3359,11 +3359,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3391,32 +3386,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127739142</v>
+        <v>127739079</v>
       </c>
       <c r="B28" t="n">
-        <v>91964</v>
+        <v>92614</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3429,13 +3424,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562991</v>
+        <v>562951</v>
       </c>
       <c r="R28" t="n">
-        <v>6355101</v>
+        <v>6355191</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3465,6 +3460,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -2070,37 +2070,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127739242</v>
+        <v>127739120</v>
       </c>
       <c r="B15" t="n">
-        <v>92614</v>
+        <v>110334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>219677</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2108,10 +2109,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563010</v>
+        <v>562926</v>
       </c>
       <c r="R15" t="n">
-        <v>6355064</v>
+        <v>6355122</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2171,38 +2172,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127739120</v>
+        <v>127739242</v>
       </c>
       <c r="B16" t="n">
-        <v>110334</v>
+        <v>92614</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219677</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562926</v>
+        <v>563010</v>
       </c>
       <c r="R16" t="n">
-        <v>6355122</v>
+        <v>6355064</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2475,37 +2475,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127739285</v>
+        <v>127739394</v>
       </c>
       <c r="B19" t="n">
-        <v>92622</v>
+        <v>96702</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2513,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563025</v>
+        <v>563102</v>
       </c>
       <c r="R19" t="n">
-        <v>6355088</v>
+        <v>6355133</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2576,38 +2577,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127739394</v>
+        <v>127739285</v>
       </c>
       <c r="B20" t="n">
-        <v>96702</v>
+        <v>92622</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563102</v>
+        <v>563025</v>
       </c>
       <c r="R20" t="n">
-        <v>6355133</v>
+        <v>6355088</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -3285,32 +3285,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127739142</v>
+        <v>127739079</v>
       </c>
       <c r="B27" t="n">
-        <v>91964</v>
+        <v>92614</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3323,13 +3323,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562991</v>
+        <v>562951</v>
       </c>
       <c r="R27" t="n">
-        <v>6355101</v>
+        <v>6355191</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3359,6 +3359,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3386,32 +3391,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127739079</v>
+        <v>127739142</v>
       </c>
       <c r="B28" t="n">
-        <v>92614</v>
+        <v>91964</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3424,13 +3429,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562951</v>
+        <v>562991</v>
       </c>
       <c r="R28" t="n">
-        <v>6355191</v>
+        <v>6355101</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3460,11 +3465,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -1357,32 +1357,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127739100</v>
+        <v>127739047</v>
       </c>
       <c r="B8" t="n">
-        <v>96702</v>
+        <v>100545</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,13 +1396,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563005</v>
+        <v>562936</v>
       </c>
       <c r="R8" t="n">
-        <v>6355183</v>
+        <v>6355216</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127739047</v>
+        <v>127739100</v>
       </c>
       <c r="B9" t="n">
-        <v>100539</v>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1498,13 +1498,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562936</v>
+        <v>563005</v>
       </c>
       <c r="R9" t="n">
-        <v>6355216</v>
+        <v>6355183</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>127739176</v>
       </c>
       <c r="B10" t="n">
-        <v>91964</v>
+        <v>91970</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>127738729</v>
       </c>
       <c r="B11" t="n">
-        <v>92640</v>
+        <v>92646</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>127738974</v>
       </c>
       <c r="B12" t="n">
-        <v>92656</v>
+        <v>92662</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>127739327</v>
       </c>
       <c r="B13" t="n">
-        <v>92656</v>
+        <v>92662</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>127739045</v>
       </c>
       <c r="B14" t="n">
-        <v>92656</v>
+        <v>92662</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,38 +2070,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127739120</v>
+        <v>127739242</v>
       </c>
       <c r="B15" t="n">
-        <v>110334</v>
+        <v>92620</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219677</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2109,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562926</v>
+        <v>563010</v>
       </c>
       <c r="R15" t="n">
-        <v>6355122</v>
+        <v>6355064</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2172,32 +2171,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127739242</v>
+        <v>127738760</v>
       </c>
       <c r="B16" t="n">
-        <v>92614</v>
+        <v>91757</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>5420</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2210,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563010</v>
+        <v>562898</v>
       </c>
       <c r="R16" t="n">
-        <v>6355064</v>
+        <v>6355174</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2273,10 +2272,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127738760</v>
+        <v>127739120</v>
       </c>
       <c r="B17" t="n">
-        <v>91751</v>
+        <v>110340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2284,26 +2283,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5420</v>
+        <v>219677</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562898</v>
+        <v>562926</v>
       </c>
       <c r="R17" t="n">
-        <v>6355174</v>
+        <v>6355122</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2377,7 +2377,7 @@
         <v>127739186</v>
       </c>
       <c r="B18" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>127739394</v>
       </c>
       <c r="B19" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>127739285</v>
       </c>
       <c r="B20" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127739175</v>
+        <v>127739305</v>
       </c>
       <c r="B21" t="n">
-        <v>92622</v>
+        <v>92662</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562997</v>
+        <v>563081</v>
       </c>
       <c r="R21" t="n">
-        <v>6355077</v>
+        <v>6355112</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2779,10 +2779,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127739305</v>
+        <v>127739175</v>
       </c>
       <c r="B22" t="n">
-        <v>92656</v>
+        <v>92628</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2790,21 +2790,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563081</v>
+        <v>562997</v>
       </c>
       <c r="R22" t="n">
-        <v>6355112</v>
+        <v>6355077</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2880,32 +2880,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127739159</v>
+        <v>127738956</v>
       </c>
       <c r="B23" t="n">
-        <v>92614</v>
+        <v>91970</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562988</v>
+        <v>562939</v>
       </c>
       <c r="R23" t="n">
-        <v>6355078</v>
+        <v>6355259</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2981,32 +2981,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127738956</v>
+        <v>127739159</v>
       </c>
       <c r="B24" t="n">
-        <v>91964</v>
+        <v>92620</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562939</v>
+        <v>562988</v>
       </c>
       <c r="R24" t="n">
-        <v>6355259</v>
+        <v>6355078</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127738941</v>
+        <v>127739160</v>
       </c>
       <c r="B25" t="n">
-        <v>105488</v>
+        <v>92628</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3093,27 +3093,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3121,13 +3120,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562981</v>
+        <v>562988</v>
       </c>
       <c r="R25" t="n">
-        <v>6355301</v>
+        <v>6355078</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3184,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127739160</v>
+        <v>127738941</v>
       </c>
       <c r="B26" t="n">
-        <v>92622</v>
+        <v>105494</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3195,26 +3194,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3222,13 +3222,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562988</v>
+        <v>562981</v>
       </c>
       <c r="R26" t="n">
-        <v>6355078</v>
+        <v>6355301</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3285,32 +3285,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127739079</v>
+        <v>127739142</v>
       </c>
       <c r="B27" t="n">
-        <v>92614</v>
+        <v>91970</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3323,13 +3323,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562951</v>
+        <v>562991</v>
       </c>
       <c r="R27" t="n">
-        <v>6355191</v>
+        <v>6355101</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3359,11 +3359,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3391,32 +3386,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127739142</v>
+        <v>127739079</v>
       </c>
       <c r="B28" t="n">
-        <v>91964</v>
+        <v>92620</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3429,13 +3424,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562991</v>
+        <v>562951</v>
       </c>
       <c r="R28" t="n">
-        <v>6355101</v>
+        <v>6355191</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3465,6 +3460,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -1360,7 +1360,7 @@
         <v>127739047</v>
       </c>
       <c r="B8" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>127739100</v>
       </c>
       <c r="B9" t="n">
-        <v>96708</v>
+        <v>96711</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>127739176</v>
       </c>
       <c r="B10" t="n">
-        <v>91970</v>
+        <v>91973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>127738729</v>
       </c>
       <c r="B11" t="n">
-        <v>92646</v>
+        <v>92649</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>127738974</v>
       </c>
       <c r="B12" t="n">
-        <v>92662</v>
+        <v>92665</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>127739327</v>
       </c>
       <c r="B13" t="n">
-        <v>92662</v>
+        <v>92665</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>127739045</v>
       </c>
       <c r="B14" t="n">
-        <v>92662</v>
+        <v>92665</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,32 +2070,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127739242</v>
+        <v>127738760</v>
       </c>
       <c r="B15" t="n">
-        <v>92620</v>
+        <v>91760</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563010</v>
+        <v>562898</v>
       </c>
       <c r="R15" t="n">
-        <v>6355064</v>
+        <v>6355174</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2171,32 +2171,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127738760</v>
+        <v>127739242</v>
       </c>
       <c r="B16" t="n">
-        <v>91757</v>
+        <v>92623</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5420</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562898</v>
+        <v>563010</v>
       </c>
       <c r="R16" t="n">
-        <v>6355174</v>
+        <v>6355064</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2275,7 +2275,7 @@
         <v>127739120</v>
       </c>
       <c r="B17" t="n">
-        <v>110340</v>
+        <v>110343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127739186</v>
       </c>
       <c r="B18" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,38 +2475,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127739394</v>
+        <v>127739285</v>
       </c>
       <c r="B19" t="n">
-        <v>96708</v>
+        <v>92631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2514,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563102</v>
+        <v>563025</v>
       </c>
       <c r="R19" t="n">
-        <v>6355133</v>
+        <v>6355088</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2577,37 +2576,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127739285</v>
+        <v>127739394</v>
       </c>
       <c r="B20" t="n">
-        <v>92628</v>
+        <v>96711</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563025</v>
+        <v>563102</v>
       </c>
       <c r="R20" t="n">
-        <v>6355088</v>
+        <v>6355133</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2681,7 +2681,7 @@
         <v>127739305</v>
       </c>
       <c r="B21" t="n">
-        <v>92662</v>
+        <v>92665</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>127739175</v>
       </c>
       <c r="B22" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>127738956</v>
       </c>
       <c r="B23" t="n">
-        <v>91970</v>
+        <v>91973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>127739159</v>
       </c>
       <c r="B24" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127739160</v>
+        <v>127738941</v>
       </c>
       <c r="B25" t="n">
-        <v>92628</v>
+        <v>105497</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3093,26 +3093,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3120,13 +3121,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562988</v>
+        <v>562981</v>
       </c>
       <c r="R25" t="n">
-        <v>6355078</v>
+        <v>6355301</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3183,10 +3184,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127738941</v>
+        <v>127739160</v>
       </c>
       <c r="B26" t="n">
-        <v>105494</v>
+        <v>92631</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,27 +3195,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3222,13 +3222,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562981</v>
+        <v>562988</v>
       </c>
       <c r="R26" t="n">
-        <v>6355301</v>
+        <v>6355078</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>127739142</v>
       </c>
       <c r="B27" t="n">
-        <v>91970</v>
+        <v>91973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>127739079</v>
       </c>
       <c r="B28" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -1357,32 +1357,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127739047</v>
+        <v>127739100</v>
       </c>
       <c r="B8" t="n">
-        <v>100548</v>
+        <v>96719</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,13 +1396,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562936</v>
+        <v>563005</v>
       </c>
       <c r="R8" t="n">
-        <v>6355216</v>
+        <v>6355183</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127739100</v>
+        <v>127739047</v>
       </c>
       <c r="B9" t="n">
-        <v>96711</v>
+        <v>100556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1498,13 +1498,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563005</v>
+        <v>562936</v>
       </c>
       <c r="R9" t="n">
-        <v>6355183</v>
+        <v>6355216</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>127739176</v>
       </c>
       <c r="B10" t="n">
-        <v>91973</v>
+        <v>91981</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>127738729</v>
       </c>
       <c r="B11" t="n">
-        <v>92649</v>
+        <v>92657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>127738974</v>
       </c>
       <c r="B12" t="n">
-        <v>92665</v>
+        <v>92673</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>127739327</v>
       </c>
       <c r="B13" t="n">
-        <v>92665</v>
+        <v>92673</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>127739045</v>
       </c>
       <c r="B14" t="n">
-        <v>92665</v>
+        <v>92673</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,10 +2070,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127738760</v>
+        <v>127739120</v>
       </c>
       <c r="B15" t="n">
-        <v>91760</v>
+        <v>110351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,26 +2081,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420</v>
+        <v>219677</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2108,10 +2109,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562898</v>
+        <v>562926</v>
       </c>
       <c r="R15" t="n">
-        <v>6355174</v>
+        <v>6355122</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2174,7 +2175,7 @@
         <v>127739242</v>
       </c>
       <c r="B16" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,10 +2273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127739120</v>
+        <v>127738760</v>
       </c>
       <c r="B17" t="n">
-        <v>110343</v>
+        <v>91768</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2283,27 +2284,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219677</v>
+        <v>5420</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562926</v>
+        <v>562898</v>
       </c>
       <c r="R17" t="n">
-        <v>6355122</v>
+        <v>6355174</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2377,7 +2377,7 @@
         <v>127739186</v>
       </c>
       <c r="B18" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>127739285</v>
       </c>
       <c r="B19" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127739394</v>
       </c>
       <c r="B20" t="n">
-        <v>96711</v>
+        <v>96719</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>127739305</v>
       </c>
       <c r="B21" t="n">
-        <v>92665</v>
+        <v>92673</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>127739175</v>
       </c>
       <c r="B22" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>127738956</v>
       </c>
       <c r="B23" t="n">
-        <v>91973</v>
+        <v>91981</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>127739159</v>
       </c>
       <c r="B24" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127738941</v>
+        <v>127739160</v>
       </c>
       <c r="B25" t="n">
-        <v>105497</v>
+        <v>92639</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3093,27 +3093,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3121,13 +3120,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562981</v>
+        <v>562988</v>
       </c>
       <c r="R25" t="n">
-        <v>6355301</v>
+        <v>6355078</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3184,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127739160</v>
+        <v>127738941</v>
       </c>
       <c r="B26" t="n">
-        <v>92631</v>
+        <v>105505</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3195,26 +3194,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3222,13 +3222,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562988</v>
+        <v>562981</v>
       </c>
       <c r="R26" t="n">
-        <v>6355078</v>
+        <v>6355301</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3285,32 +3285,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127739142</v>
+        <v>127739079</v>
       </c>
       <c r="B27" t="n">
-        <v>91973</v>
+        <v>92631</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3323,13 +3323,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562991</v>
+        <v>562951</v>
       </c>
       <c r="R27" t="n">
-        <v>6355101</v>
+        <v>6355191</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3359,6 +3359,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3386,32 +3391,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127739079</v>
+        <v>127739142</v>
       </c>
       <c r="B28" t="n">
-        <v>92623</v>
+        <v>91981</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3424,13 +3429,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562951</v>
+        <v>562991</v>
       </c>
       <c r="R28" t="n">
-        <v>6355191</v>
+        <v>6355101</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3460,11 +3465,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -1360,7 +1360,7 @@
         <v>127739100</v>
       </c>
       <c r="B8" t="n">
-        <v>96719</v>
+        <v>96720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>127739047</v>
       </c>
       <c r="B9" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>127739176</v>
       </c>
       <c r="B10" t="n">
-        <v>91981</v>
+        <v>91982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>127738729</v>
       </c>
       <c r="B11" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>127738974</v>
       </c>
       <c r="B12" t="n">
-        <v>92673</v>
+        <v>92674</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>127739327</v>
       </c>
       <c r="B13" t="n">
-        <v>92673</v>
+        <v>92674</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>127739045</v>
       </c>
       <c r="B14" t="n">
-        <v>92673</v>
+        <v>92674</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,10 +2070,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127739120</v>
+        <v>127738760</v>
       </c>
       <c r="B15" t="n">
-        <v>110351</v>
+        <v>91769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,27 +2081,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219677</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2109,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562926</v>
+        <v>562898</v>
       </c>
       <c r="R15" t="n">
-        <v>6355122</v>
+        <v>6355174</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2172,37 +2171,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127739242</v>
+        <v>127739120</v>
       </c>
       <c r="B16" t="n">
-        <v>92631</v>
+        <v>110352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>219677</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563010</v>
+        <v>562926</v>
       </c>
       <c r="R16" t="n">
-        <v>6355064</v>
+        <v>6355122</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2273,32 +2273,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127738760</v>
+        <v>127739242</v>
       </c>
       <c r="B17" t="n">
-        <v>91768</v>
+        <v>92632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5420</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562898</v>
+        <v>563010</v>
       </c>
       <c r="R17" t="n">
-        <v>6355174</v>
+        <v>6355064</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2377,7 +2377,7 @@
         <v>127739186</v>
       </c>
       <c r="B18" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,37 +2475,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127739285</v>
+        <v>127739394</v>
       </c>
       <c r="B19" t="n">
-        <v>92639</v>
+        <v>96720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2513,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563025</v>
+        <v>563102</v>
       </c>
       <c r="R19" t="n">
-        <v>6355088</v>
+        <v>6355133</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2576,38 +2577,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127739394</v>
+        <v>127739285</v>
       </c>
       <c r="B20" t="n">
-        <v>96719</v>
+        <v>92640</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563102</v>
+        <v>563025</v>
       </c>
       <c r="R20" t="n">
-        <v>6355133</v>
+        <v>6355088</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127739305</v>
+        <v>127739175</v>
       </c>
       <c r="B21" t="n">
-        <v>92673</v>
+        <v>92640</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563081</v>
+        <v>562997</v>
       </c>
       <c r="R21" t="n">
-        <v>6355112</v>
+        <v>6355077</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2779,10 +2779,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127739175</v>
+        <v>127739305</v>
       </c>
       <c r="B22" t="n">
-        <v>92639</v>
+        <v>92674</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2790,21 +2790,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562997</v>
+        <v>563081</v>
       </c>
       <c r="R22" t="n">
-        <v>6355077</v>
+        <v>6355112</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2880,32 +2880,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127738956</v>
+        <v>127739159</v>
       </c>
       <c r="B23" t="n">
-        <v>91981</v>
+        <v>92632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562939</v>
+        <v>562988</v>
       </c>
       <c r="R23" t="n">
-        <v>6355259</v>
+        <v>6355078</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2981,32 +2981,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127739159</v>
+        <v>127738956</v>
       </c>
       <c r="B24" t="n">
-        <v>92631</v>
+        <v>91982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562988</v>
+        <v>562939</v>
       </c>
       <c r="R24" t="n">
-        <v>6355078</v>
+        <v>6355259</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127739160</v>
+        <v>127738941</v>
       </c>
       <c r="B25" t="n">
-        <v>92639</v>
+        <v>105506</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3093,26 +3093,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3120,13 +3121,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562988</v>
+        <v>562981</v>
       </c>
       <c r="R25" t="n">
-        <v>6355078</v>
+        <v>6355301</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3183,10 +3184,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127738941</v>
+        <v>127739160</v>
       </c>
       <c r="B26" t="n">
-        <v>105505</v>
+        <v>92640</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,27 +3195,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3222,13 +3222,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562981</v>
+        <v>562988</v>
       </c>
       <c r="R26" t="n">
-        <v>6355301</v>
+        <v>6355078</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3285,32 +3285,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127739079</v>
+        <v>127739142</v>
       </c>
       <c r="B27" t="n">
-        <v>92631</v>
+        <v>91982</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3323,13 +3323,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562951</v>
+        <v>562991</v>
       </c>
       <c r="R27" t="n">
-        <v>6355191</v>
+        <v>6355101</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3359,11 +3359,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3391,32 +3386,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127739142</v>
+        <v>127739079</v>
       </c>
       <c r="B28" t="n">
-        <v>91981</v>
+        <v>92632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3429,13 +3424,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562991</v>
+        <v>562951</v>
       </c>
       <c r="R28" t="n">
-        <v>6355101</v>
+        <v>6355191</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3465,6 +3460,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -2070,32 +2070,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127738760</v>
+        <v>127739242</v>
       </c>
       <c r="B15" t="n">
-        <v>91769</v>
+        <v>92632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562898</v>
+        <v>563010</v>
       </c>
       <c r="R15" t="n">
-        <v>6355174</v>
+        <v>6355064</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127739120</v>
+        <v>127738760</v>
       </c>
       <c r="B16" t="n">
-        <v>110352</v>
+        <v>91769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,27 +2182,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219677</v>
+        <v>5420</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2210,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562926</v>
+        <v>562898</v>
       </c>
       <c r="R16" t="n">
-        <v>6355122</v>
+        <v>6355174</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2273,37 +2272,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127739242</v>
+        <v>127739120</v>
       </c>
       <c r="B17" t="n">
-        <v>92632</v>
+        <v>110352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>219677</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563010</v>
+        <v>562926</v>
       </c>
       <c r="R17" t="n">
-        <v>6355064</v>
+        <v>6355122</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127738941</v>
+        <v>127739160</v>
       </c>
       <c r="B25" t="n">
-        <v>105506</v>
+        <v>92640</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3093,27 +3093,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3121,13 +3120,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562981</v>
+        <v>562988</v>
       </c>
       <c r="R25" t="n">
-        <v>6355301</v>
+        <v>6355078</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3184,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127739160</v>
+        <v>127738941</v>
       </c>
       <c r="B26" t="n">
-        <v>92640</v>
+        <v>105506</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3195,26 +3194,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3222,13 +3222,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562988</v>
+        <v>562981</v>
       </c>
       <c r="R26" t="n">
-        <v>6355078</v>
+        <v>6355301</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3285,32 +3285,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127739142</v>
+        <v>127739079</v>
       </c>
       <c r="B27" t="n">
-        <v>91982</v>
+        <v>92632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3323,13 +3323,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562991</v>
+        <v>562951</v>
       </c>
       <c r="R27" t="n">
-        <v>6355101</v>
+        <v>6355191</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3359,6 +3359,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3386,32 +3391,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127739079</v>
+        <v>127739142</v>
       </c>
       <c r="B28" t="n">
-        <v>92632</v>
+        <v>91982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3424,13 +3429,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562951</v>
+        <v>562991</v>
       </c>
       <c r="R28" t="n">
-        <v>6355191</v>
+        <v>6355101</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3460,11 +3465,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -1360,7 +1360,7 @@
         <v>127739100</v>
       </c>
       <c r="B8" t="n">
-        <v>96720</v>
+        <v>96721</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>127739047</v>
       </c>
       <c r="B9" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>127739176</v>
       </c>
       <c r="B10" t="n">
-        <v>91982</v>
+        <v>91983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>127738729</v>
       </c>
       <c r="B11" t="n">
-        <v>92658</v>
+        <v>92659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>127738974</v>
       </c>
       <c r="B12" t="n">
-        <v>92674</v>
+        <v>92675</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>127739327</v>
       </c>
       <c r="B13" t="n">
-        <v>92674</v>
+        <v>92675</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>127739045</v>
       </c>
       <c r="B14" t="n">
-        <v>92674</v>
+        <v>92675</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>127739242</v>
       </c>
       <c r="B15" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>127738760</v>
       </c>
       <c r="B16" t="n">
-        <v>91769</v>
+        <v>91770</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>127739120</v>
       </c>
       <c r="B17" t="n">
-        <v>110352</v>
+        <v>110353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127739186</v>
       </c>
       <c r="B18" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>127739394</v>
       </c>
       <c r="B19" t="n">
-        <v>96720</v>
+        <v>96721</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>127739285</v>
       </c>
       <c r="B20" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>127739175</v>
       </c>
       <c r="B21" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>127739305</v>
       </c>
       <c r="B22" t="n">
-        <v>92674</v>
+        <v>92675</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2880,32 +2880,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127739159</v>
+        <v>127738956</v>
       </c>
       <c r="B23" t="n">
-        <v>92632</v>
+        <v>91983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562988</v>
+        <v>562939</v>
       </c>
       <c r="R23" t="n">
-        <v>6355078</v>
+        <v>6355259</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2981,32 +2981,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127738956</v>
+        <v>127739159</v>
       </c>
       <c r="B24" t="n">
-        <v>91982</v>
+        <v>92633</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562939</v>
+        <v>562988</v>
       </c>
       <c r="R24" t="n">
-        <v>6355259</v>
+        <v>6355078</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3085,7 +3085,7 @@
         <v>127739160</v>
       </c>
       <c r="B25" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>127738941</v>
       </c>
       <c r="B26" t="n">
-        <v>105506</v>
+        <v>105507</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>127739079</v>
       </c>
       <c r="B27" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>127739142</v>
       </c>
       <c r="B28" t="n">
-        <v>91982</v>
+        <v>91983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -1360,7 +1360,7 @@
         <v>127739100</v>
       </c>
       <c r="B8" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>127739047</v>
       </c>
       <c r="B9" t="n">
-        <v>100558</v>
+        <v>100559</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>127739176</v>
       </c>
       <c r="B10" t="n">
-        <v>91983</v>
+        <v>91984</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>127738729</v>
       </c>
       <c r="B11" t="n">
-        <v>92659</v>
+        <v>92660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>127738974</v>
       </c>
       <c r="B12" t="n">
-        <v>92675</v>
+        <v>92676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>127739327</v>
       </c>
       <c r="B13" t="n">
-        <v>92675</v>
+        <v>92676</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>127739045</v>
       </c>
       <c r="B14" t="n">
-        <v>92675</v>
+        <v>92676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,37 +2070,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127739242</v>
+        <v>127739120</v>
       </c>
       <c r="B15" t="n">
-        <v>92633</v>
+        <v>110354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>219677</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2108,10 +2109,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563010</v>
+        <v>562926</v>
       </c>
       <c r="R15" t="n">
-        <v>6355064</v>
+        <v>6355122</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2171,32 +2172,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127738760</v>
+        <v>127739242</v>
       </c>
       <c r="B16" t="n">
-        <v>91770</v>
+        <v>92634</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5420</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2210,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562898</v>
+        <v>563010</v>
       </c>
       <c r="R16" t="n">
-        <v>6355174</v>
+        <v>6355064</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2272,10 +2273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127739120</v>
+        <v>127738760</v>
       </c>
       <c r="B17" t="n">
-        <v>110353</v>
+        <v>91771</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2283,27 +2284,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219677</v>
+        <v>5420</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562926</v>
+        <v>562898</v>
       </c>
       <c r="R17" t="n">
-        <v>6355122</v>
+        <v>6355174</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2377,7 +2377,7 @@
         <v>127739186</v>
       </c>
       <c r="B18" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>127739394</v>
       </c>
       <c r="B19" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>127739285</v>
       </c>
       <c r="B20" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>127739175</v>
       </c>
       <c r="B21" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>127739305</v>
       </c>
       <c r="B22" t="n">
-        <v>92675</v>
+        <v>92676</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2880,32 +2880,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127738956</v>
+        <v>127739159</v>
       </c>
       <c r="B23" t="n">
-        <v>91983</v>
+        <v>92634</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562939</v>
+        <v>562988</v>
       </c>
       <c r="R23" t="n">
-        <v>6355259</v>
+        <v>6355078</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2981,32 +2981,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127739159</v>
+        <v>127738956</v>
       </c>
       <c r="B24" t="n">
-        <v>92633</v>
+        <v>91984</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562988</v>
+        <v>562939</v>
       </c>
       <c r="R24" t="n">
-        <v>6355078</v>
+        <v>6355259</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3085,7 +3085,7 @@
         <v>127739160</v>
       </c>
       <c r="B25" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>127738941</v>
       </c>
       <c r="B26" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>127739079</v>
       </c>
       <c r="B27" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>127739142</v>
       </c>
       <c r="B28" t="n">
-        <v>91983</v>
+        <v>91984</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -2070,10 +2070,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127739120</v>
+        <v>127738760</v>
       </c>
       <c r="B15" t="n">
-        <v>110354</v>
+        <v>91771</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,27 +2081,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219677</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2109,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562926</v>
+        <v>562898</v>
       </c>
       <c r="R15" t="n">
-        <v>6355122</v>
+        <v>6355174</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2172,37 +2171,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127739242</v>
+        <v>127739120</v>
       </c>
       <c r="B16" t="n">
-        <v>92634</v>
+        <v>110354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>219677</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563010</v>
+        <v>562926</v>
       </c>
       <c r="R16" t="n">
-        <v>6355064</v>
+        <v>6355122</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2273,32 +2273,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127738760</v>
+        <v>127739242</v>
       </c>
       <c r="B17" t="n">
-        <v>91771</v>
+        <v>92634</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5420</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562898</v>
+        <v>563010</v>
       </c>
       <c r="R17" t="n">
-        <v>6355174</v>
+        <v>6355064</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2475,38 +2475,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127739394</v>
+        <v>127739285</v>
       </c>
       <c r="B19" t="n">
-        <v>96722</v>
+        <v>92642</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2514,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563102</v>
+        <v>563025</v>
       </c>
       <c r="R19" t="n">
-        <v>6355133</v>
+        <v>6355088</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2577,37 +2576,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127739285</v>
+        <v>127739394</v>
       </c>
       <c r="B20" t="n">
-        <v>92642</v>
+        <v>96722</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563025</v>
+        <v>563102</v>
       </c>
       <c r="R20" t="n">
-        <v>6355088</v>
+        <v>6355133</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -2070,32 +2070,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127738760</v>
+        <v>127739242</v>
       </c>
       <c r="B15" t="n">
-        <v>91771</v>
+        <v>92634</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562898</v>
+        <v>563010</v>
       </c>
       <c r="R15" t="n">
-        <v>6355174</v>
+        <v>6355064</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127739120</v>
+        <v>127738760</v>
       </c>
       <c r="B16" t="n">
-        <v>110354</v>
+        <v>91771</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,27 +2182,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219677</v>
+        <v>5420</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2210,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562926</v>
+        <v>562898</v>
       </c>
       <c r="R16" t="n">
-        <v>6355122</v>
+        <v>6355174</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2273,37 +2272,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127739242</v>
+        <v>127739120</v>
       </c>
       <c r="B17" t="n">
-        <v>92634</v>
+        <v>110354</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>219677</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563010</v>
+        <v>562926</v>
       </c>
       <c r="R17" t="n">
-        <v>6355064</v>
+        <v>6355122</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -2070,32 +2070,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127739242</v>
+        <v>127738760</v>
       </c>
       <c r="B15" t="n">
-        <v>92634</v>
+        <v>91771</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563010</v>
+        <v>562898</v>
       </c>
       <c r="R15" t="n">
-        <v>6355064</v>
+        <v>6355174</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127738760</v>
+        <v>127739120</v>
       </c>
       <c r="B16" t="n">
-        <v>91771</v>
+        <v>110354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,26 +2182,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5420</v>
+        <v>219677</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2209,10 +2210,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562898</v>
+        <v>562926</v>
       </c>
       <c r="R16" t="n">
-        <v>6355174</v>
+        <v>6355122</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2272,38 +2273,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127739120</v>
+        <v>127739242</v>
       </c>
       <c r="B17" t="n">
-        <v>110354</v>
+        <v>92634</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219677</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562926</v>
+        <v>563010</v>
       </c>
       <c r="R17" t="n">
-        <v>6355122</v>
+        <v>6355064</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -1357,32 +1357,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127739100</v>
+        <v>127739047</v>
       </c>
       <c r="B8" t="n">
-        <v>96722</v>
+        <v>100567</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,13 +1396,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563005</v>
+        <v>562936</v>
       </c>
       <c r="R8" t="n">
-        <v>6355183</v>
+        <v>6355216</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127739047</v>
+        <v>127739100</v>
       </c>
       <c r="B9" t="n">
-        <v>100559</v>
+        <v>96730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1498,13 +1498,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562936</v>
+        <v>563005</v>
       </c>
       <c r="R9" t="n">
-        <v>6355216</v>
+        <v>6355183</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>127739176</v>
       </c>
       <c r="B10" t="n">
-        <v>91984</v>
+        <v>91992</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>127738729</v>
       </c>
       <c r="B11" t="n">
-        <v>92660</v>
+        <v>92668</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>127738974</v>
       </c>
       <c r="B12" t="n">
-        <v>92676</v>
+        <v>92684</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>127739327</v>
       </c>
       <c r="B13" t="n">
-        <v>92676</v>
+        <v>92684</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>127739045</v>
       </c>
       <c r="B14" t="n">
-        <v>92676</v>
+        <v>92684</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,32 +2070,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127739242</v>
+        <v>127738760</v>
       </c>
       <c r="B15" t="n">
-        <v>92634</v>
+        <v>91779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563010</v>
+        <v>562898</v>
       </c>
       <c r="R15" t="n">
-        <v>6355064</v>
+        <v>6355174</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2171,32 +2171,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127738760</v>
+        <v>127739242</v>
       </c>
       <c r="B16" t="n">
-        <v>91771</v>
+        <v>92642</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5420</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562898</v>
+        <v>563010</v>
       </c>
       <c r="R16" t="n">
-        <v>6355174</v>
+        <v>6355064</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2275,7 +2275,7 @@
         <v>127739120</v>
       </c>
       <c r="B17" t="n">
-        <v>110354</v>
+        <v>110362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127739186</v>
       </c>
       <c r="B18" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,37 +2475,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127739285</v>
+        <v>127739394</v>
       </c>
       <c r="B19" t="n">
-        <v>92642</v>
+        <v>96730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2513,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563025</v>
+        <v>563102</v>
       </c>
       <c r="R19" t="n">
-        <v>6355088</v>
+        <v>6355133</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2576,38 +2577,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127739394</v>
+        <v>127739285</v>
       </c>
       <c r="B20" t="n">
-        <v>96722</v>
+        <v>92650</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563102</v>
+        <v>563025</v>
       </c>
       <c r="R20" t="n">
-        <v>6355133</v>
+        <v>6355088</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127739175</v>
+        <v>127739305</v>
       </c>
       <c r="B21" t="n">
-        <v>92642</v>
+        <v>92684</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562997</v>
+        <v>563081</v>
       </c>
       <c r="R21" t="n">
-        <v>6355077</v>
+        <v>6355112</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2779,10 +2779,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127739305</v>
+        <v>127739175</v>
       </c>
       <c r="B22" t="n">
-        <v>92676</v>
+        <v>92650</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2790,21 +2790,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563081</v>
+        <v>562997</v>
       </c>
       <c r="R22" t="n">
-        <v>6355112</v>
+        <v>6355077</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2880,32 +2880,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127739159</v>
+        <v>127738956</v>
       </c>
       <c r="B23" t="n">
-        <v>92634</v>
+        <v>91992</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562988</v>
+        <v>562939</v>
       </c>
       <c r="R23" t="n">
-        <v>6355078</v>
+        <v>6355259</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2981,32 +2981,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127738956</v>
+        <v>127739159</v>
       </c>
       <c r="B24" t="n">
-        <v>91984</v>
+        <v>92642</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562939</v>
+        <v>562988</v>
       </c>
       <c r="R24" t="n">
-        <v>6355259</v>
+        <v>6355078</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3085,7 +3085,7 @@
         <v>127739160</v>
       </c>
       <c r="B25" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>127738941</v>
       </c>
       <c r="B26" t="n">
-        <v>105508</v>
+        <v>105516</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3285,32 +3285,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127739079</v>
+        <v>127739142</v>
       </c>
       <c r="B27" t="n">
-        <v>92634</v>
+        <v>91992</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3323,13 +3323,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562951</v>
+        <v>562991</v>
       </c>
       <c r="R27" t="n">
-        <v>6355191</v>
+        <v>6355101</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3359,11 +3359,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3391,32 +3386,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127739142</v>
+        <v>127739079</v>
       </c>
       <c r="B28" t="n">
-        <v>91984</v>
+        <v>92642</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3429,13 +3424,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562991</v>
+        <v>562951</v>
       </c>
       <c r="R28" t="n">
-        <v>6355101</v>
+        <v>6355191</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3465,6 +3460,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -1357,32 +1357,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127739047</v>
+        <v>127739100</v>
       </c>
       <c r="B8" t="n">
-        <v>100567</v>
+        <v>96823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,13 +1396,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562936</v>
+        <v>563005</v>
       </c>
       <c r="R8" t="n">
-        <v>6355216</v>
+        <v>6355183</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127739100</v>
+        <v>127739047</v>
       </c>
       <c r="B9" t="n">
-        <v>96730</v>
+        <v>100660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1498,13 +1498,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563005</v>
+        <v>562936</v>
       </c>
       <c r="R9" t="n">
-        <v>6355183</v>
+        <v>6355216</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>127739176</v>
       </c>
       <c r="B10" t="n">
-        <v>91992</v>
+        <v>92084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>127738729</v>
       </c>
       <c r="B11" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>127738974</v>
       </c>
       <c r="B12" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>127739327</v>
       </c>
       <c r="B13" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>127739045</v>
       </c>
       <c r="B14" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>127738760</v>
       </c>
       <c r="B15" t="n">
-        <v>91779</v>
+        <v>91871</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>127739242</v>
       </c>
       <c r="B16" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>127739120</v>
       </c>
       <c r="B17" t="n">
-        <v>110362</v>
+        <v>110455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127739186</v>
       </c>
       <c r="B18" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,38 +2475,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127739394</v>
+        <v>127739285</v>
       </c>
       <c r="B19" t="n">
-        <v>96730</v>
+        <v>92742</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2514,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563102</v>
+        <v>563025</v>
       </c>
       <c r="R19" t="n">
-        <v>6355133</v>
+        <v>6355088</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2577,37 +2576,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127739285</v>
+        <v>127739394</v>
       </c>
       <c r="B20" t="n">
-        <v>92650</v>
+        <v>96823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563025</v>
+        <v>563102</v>
       </c>
       <c r="R20" t="n">
-        <v>6355088</v>
+        <v>6355133</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2681,7 +2681,7 @@
         <v>127739305</v>
       </c>
       <c r="B21" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>127739175</v>
       </c>
       <c r="B22" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2880,32 +2880,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127738956</v>
+        <v>127739159</v>
       </c>
       <c r="B23" t="n">
-        <v>91992</v>
+        <v>92734</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562939</v>
+        <v>562988</v>
       </c>
       <c r="R23" t="n">
-        <v>6355259</v>
+        <v>6355078</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2981,32 +2981,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127739159</v>
+        <v>127738956</v>
       </c>
       <c r="B24" t="n">
-        <v>92642</v>
+        <v>92084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562988</v>
+        <v>562939</v>
       </c>
       <c r="R24" t="n">
-        <v>6355078</v>
+        <v>6355259</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3085,7 +3085,7 @@
         <v>127739160</v>
       </c>
       <c r="B25" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>127738941</v>
       </c>
       <c r="B26" t="n">
-        <v>105516</v>
+        <v>105609</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3285,32 +3285,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127739142</v>
+        <v>127739079</v>
       </c>
       <c r="B27" t="n">
-        <v>91992</v>
+        <v>92734</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3323,13 +3323,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562991</v>
+        <v>562951</v>
       </c>
       <c r="R27" t="n">
-        <v>6355101</v>
+        <v>6355191</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3359,6 +3359,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3386,32 +3391,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127739079</v>
+        <v>127739142</v>
       </c>
       <c r="B28" t="n">
-        <v>92642</v>
+        <v>92084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3424,13 +3429,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562951</v>
+        <v>562991</v>
       </c>
       <c r="R28" t="n">
-        <v>6355191</v>
+        <v>6355101</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3460,11 +3465,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97387083</v>
+        <v>97387026</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562934.1621092594</v>
+        <v>563064</v>
       </c>
       <c r="R2" t="n">
-        <v>6355212.073105412</v>
+        <v>6355136</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mindre förekomst på murken granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97387026</v>
+        <v>97387036</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563064.0487061769</v>
+        <v>562880</v>
       </c>
       <c r="R3" t="n">
-        <v>6355136.875739826</v>
+        <v>6355160</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -857,27 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Mindre förekomst på murken granlåga</t>
+          <t>Mindre förekomst på klen murken låga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,53 +879,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97387080</v>
+        <v>127739100</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Vädern, Sm</t>
+          <t>St. Bråbo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562932.238639978</v>
+        <v>563005</v>
       </c>
       <c r="R4" t="n">
-        <v>6355337.279475265</v>
+        <v>6355183</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,22 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,71 +962,71 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97387066</v>
+        <v>127739394</v>
       </c>
       <c r="B5" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stora Vädern, Sm</t>
+          <t>St. Bråbo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562978.5436544381</v>
+        <v>563102</v>
       </c>
       <c r="R5" t="n">
-        <v>6355174.967691078</v>
+        <v>6355133</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,27 +1050,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mindre förekomst på block</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,68 +1064,69 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97387027</v>
+        <v>97387061</v>
       </c>
       <c r="B6" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>2014</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Vädern, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563012.3871049697</v>
+        <v>562881</v>
       </c>
       <c r="R6" t="n">
-        <v>6355190.06330972</v>
+        <v>6355153</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1203,22 +1153,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En handfull små fruktkroppar på asplåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,15 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103322174</v>
+        <v>97387066</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stockklinteberg, Sm</t>
+          <t>Stora Vädern, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562953.8132512463</v>
+        <v>562979</v>
       </c>
       <c r="R7" t="n">
-        <v>6355235.587159257</v>
+        <v>6355175</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,22 +1255,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-04-27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-04-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mindre förekomst på block</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,22 +1280,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127739100</v>
+        <v>127739079</v>
       </c>
       <c r="B8" t="n">
-        <v>96823</v>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,27 +1303,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,13 +1330,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563005</v>
+        <v>562951</v>
       </c>
       <c r="R8" t="n">
-        <v>6355183</v>
+        <v>6355191</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,6 +1366,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar inom 1 m2.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,38 +1398,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127739047</v>
+        <v>127739159</v>
       </c>
       <c r="B9" t="n">
-        <v>100660</v>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1498,13 +1436,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562936</v>
+        <v>562988</v>
       </c>
       <c r="R9" t="n">
-        <v>6355216</v>
+        <v>6355078</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1561,32 +1499,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127739176</v>
+        <v>127739242</v>
       </c>
       <c r="B10" t="n">
-        <v>92084</v>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562997</v>
+        <v>563010</v>
       </c>
       <c r="R10" t="n">
-        <v>6355077</v>
+        <v>6355064</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1662,10 +1600,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127738729</v>
+        <v>127739160</v>
       </c>
       <c r="B11" t="n">
-        <v>92760</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,28 +1611,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4368</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1704,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562900</v>
+        <v>562988</v>
       </c>
       <c r="R11" t="n">
-        <v>6355069</v>
+        <v>6355078</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1767,32 +1701,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127738974</v>
+        <v>127739175</v>
       </c>
       <c r="B12" t="n">
-        <v>92776</v>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562931</v>
+        <v>562997</v>
       </c>
       <c r="R12" t="n">
-        <v>6355226</v>
+        <v>6355077</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1868,32 +1802,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127739327</v>
+        <v>127739186</v>
       </c>
       <c r="B13" t="n">
-        <v>92776</v>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1906,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563097</v>
+        <v>563004</v>
       </c>
       <c r="R13" t="n">
-        <v>6355118</v>
+        <v>6355079</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1969,32 +1903,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127739045</v>
+        <v>127739264</v>
       </c>
       <c r="B14" t="n">
-        <v>92776</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +1941,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562936</v>
+        <v>563034</v>
       </c>
       <c r="R14" t="n">
-        <v>6355216</v>
+        <v>6355055</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,32 +2004,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127738760</v>
+        <v>127739285</v>
       </c>
       <c r="B15" t="n">
-        <v>91871</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,13 +2042,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562898</v>
+        <v>563025</v>
       </c>
       <c r="R15" t="n">
-        <v>6355174</v>
+        <v>6355088</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2171,10 +2105,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127739242</v>
+        <v>127738729</v>
       </c>
       <c r="B16" t="n">
-        <v>92734</v>
+        <v>93215</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,24 +2116,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>4368</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2209,13 +2147,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563010</v>
+        <v>562900</v>
       </c>
       <c r="R16" t="n">
-        <v>6355064</v>
+        <v>6355069</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2272,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127739120</v>
+        <v>127738760</v>
       </c>
       <c r="B17" t="n">
-        <v>110455</v>
+        <v>92348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2283,27 +2221,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219677</v>
+        <v>5420</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2311,10 +2248,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562926</v>
+        <v>562898</v>
       </c>
       <c r="R17" t="n">
-        <v>6355122</v>
+        <v>6355174</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2374,32 +2311,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127739186</v>
+        <v>127738708</v>
       </c>
       <c r="B18" t="n">
-        <v>92742</v>
+        <v>93233</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,13 +2349,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563004</v>
+        <v>562881</v>
       </c>
       <c r="R18" t="n">
-        <v>6355079</v>
+        <v>6354997</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2475,32 +2412,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127739285</v>
+        <v>127738974</v>
       </c>
       <c r="B19" t="n">
-        <v>92742</v>
+        <v>93233</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2513,13 +2450,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563025</v>
+        <v>562931</v>
       </c>
       <c r="R19" t="n">
-        <v>6355088</v>
+        <v>6355226</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2576,10 +2513,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127739394</v>
+        <v>127739045</v>
       </c>
       <c r="B20" t="n">
-        <v>96823</v>
+        <v>93233</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2587,27 +2524,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2615,13 +2551,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563102</v>
+        <v>562936</v>
       </c>
       <c r="R20" t="n">
-        <v>6355133</v>
+        <v>6355216</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2681,11 +2617,11 @@
         <v>127739305</v>
       </c>
       <c r="B21" t="n">
-        <v>92776</v>
+        <v>93233</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2779,32 +2715,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127739175</v>
+        <v>127739327</v>
       </c>
       <c r="B22" t="n">
-        <v>92742</v>
+        <v>93233</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2817,13 +2753,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562997</v>
+        <v>563097</v>
       </c>
       <c r="R22" t="n">
-        <v>6355077</v>
+        <v>6355118</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2880,32 +2816,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127739159</v>
+        <v>127738956</v>
       </c>
       <c r="B23" t="n">
-        <v>92734</v>
+        <v>92567</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2918,10 +2854,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562988</v>
+        <v>562939</v>
       </c>
       <c r="R23" t="n">
-        <v>6355078</v>
+        <v>6355259</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2981,10 +2917,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127738956</v>
+        <v>127739142</v>
       </c>
       <c r="B24" t="n">
-        <v>92084</v>
+        <v>92567</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3019,13 +2955,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562939</v>
+        <v>562991</v>
       </c>
       <c r="R24" t="n">
-        <v>6355259</v>
+        <v>6355101</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3082,10 +3018,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127739160</v>
+        <v>127739176</v>
       </c>
       <c r="B25" t="n">
-        <v>92742</v>
+        <v>92567</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3093,21 +3029,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3120,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562988</v>
+        <v>562997</v>
       </c>
       <c r="R25" t="n">
-        <v>6355078</v>
+        <v>6355077</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3183,10 +3119,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127738941</v>
+        <v>97387463</v>
       </c>
       <c r="B26" t="n">
-        <v>105609</v>
+        <v>57132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,41 +3130,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>St. Bråbo, Sm</t>
+          <t>Stora Vädern, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562981</v>
+        <v>563120</v>
       </c>
       <c r="R26" t="n">
-        <v>6355301</v>
+        <v>6355173</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3252,12 +3193,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>äter knoppar i toppen av klibbal, ovanligt orädd</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3266,70 +3222,71 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127739079</v>
+        <v>97387476</v>
       </c>
       <c r="B27" t="n">
-        <v>92734</v>
+        <v>57947</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>102977</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>St. Bråbo, Sm</t>
+          <t>Stora Vädern, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562951</v>
+        <v>562962</v>
       </c>
       <c r="R27" t="n">
-        <v>6355191</v>
+        <v>6355193</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3353,17 +3310,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>3 fruktkroppar inom 1 m2.</t>
+          <t>Spår, utgrävd myrstack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3372,56 +3339,56 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127739142</v>
+        <v>127739355</v>
       </c>
       <c r="B28" t="n">
-        <v>92084</v>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6031</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3429,13 +3396,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562991</v>
+        <v>563111</v>
       </c>
       <c r="R28" t="n">
-        <v>6355101</v>
+        <v>6355129</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3473,7 +3440,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3489,6 +3455,1006 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>97387090</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stora Vädern, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>563101</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6355100</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gnag på liggande död glasbjörk</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127739120</v>
+      </c>
+      <c r="B30" t="n">
+        <v>111176</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>562926</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6355122</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127739266</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>563034</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6355055</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127738941</v>
+      </c>
+      <c r="B32" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>562981</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6355301</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>97387027</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stora Vädern, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>563012</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6355190</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>97387080</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stora Vädern, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>562933</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6355337</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>97387081</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stora Vädern, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>562862</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6355075</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>97387083</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stora Vädern, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>562934</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6355212</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>103322174</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stockklinteberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>562954</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6355236</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-04-27</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-04-27</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127739047</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>St. Bråbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>562936</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6355216</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40522-2023 artfynd.xlsx
+++ b/artfynd/A 40522-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387036</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739100</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739394</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387061</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387066</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1395,6 +1430,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739079</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739159</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1597,6 +1642,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739242</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739160</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739175</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1900,6 +1960,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739186</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739264</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2102,6 +2172,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739285</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2207,6 +2282,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127738729</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2308,6 +2388,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127738760</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2409,6 +2494,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127738708</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2510,6 +2600,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127738974</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2611,6 +2706,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739045</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739305</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2813,6 +2918,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739327</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2914,6 +3024,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127738956</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3015,6 +3130,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739142</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3116,6 +3236,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739176</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3237,6 +3362,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387463</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3354,6 +3484,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387476</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3455,6 +3590,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739355</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3562,6 +3702,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387090</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3664,6 +3809,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739120</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3766,6 +3916,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739266</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3868,6 +4023,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127738941</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3965,6 +4125,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387027</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4062,6 +4227,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387080</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4159,6 +4329,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387081</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4256,6 +4431,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97387083</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4353,6 +4533,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103322174</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4455,8 +4640,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739047</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>